--- a/output/Shandong/菏泽市_news.xlsx
+++ b/output/Shandong/菏泽市_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P106"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,9 +551,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>True</t>
@@ -565,14 +563,12 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>883</v>
+        <v>1044</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/0bff82986bac40588721edbcce204dbf/detail</t>
@@ -621,9 +617,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>True</t>
@@ -635,14 +629,12 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>706</v>
+        <v>854</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/283b1af20fbd44d0b262748de8f1db9a/detail</t>
@@ -691,9 +683,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>True</t>
@@ -705,14 +695,12 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6127</v>
+        <v>6263</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/c838651567db46cfb89fe5b5b5664226/detail</t>
@@ -761,9 +749,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>True</t>
@@ -775,14 +761,12 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6155</v>
+        <v>6293</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/f6600554d1b443d8a967350a81b80a6c/detail</t>
@@ -831,9 +815,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>True</t>
@@ -845,14 +827,12 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5683</v>
+        <v>5827</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/97d5205899f94af786fab1eda19aa7a2/detail</t>
@@ -901,9 +881,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>True</t>
@@ -915,14 +893,12 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7173</v>
+        <v>7313</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/94a28c6b92924ca789326b2044818f21/detail</t>
@@ -971,9 +947,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>True</t>
@@ -985,14 +959,12 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7455</v>
+        <v>7601</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/61c54bdd6c3b4bf6af8ee14425e9fa97/detail</t>
@@ -1041,9 +1013,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>True</t>
@@ -1055,14 +1025,12 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3942</v>
+        <v>4083</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/b0ec3b3f7fb342a29f51c1979a7e67f3/detail</t>
@@ -1111,9 +1079,7 @@
           <t>有条件开放</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>True</t>
@@ -1125,14 +1091,12 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3872</v>
+        <v>4015</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/d8d9443488364b0dadd96db86bd4fcf2/detail</t>
@@ -1181,9 +1145,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>True</t>
@@ -1195,14 +1157,12 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1863</v>
+        <v>2001</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/b09409f78dda44b8a109fd11e9c39513/detail</t>
@@ -1251,9 +1211,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>True</t>
@@ -1265,14 +1223,12 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/c65dc81e89984f819b34d33bf4be2279/detail</t>
@@ -1321,9 +1277,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>True</t>
@@ -1335,14 +1289,12 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/8e17c60368cf430e9da884f994e92592/detail</t>
@@ -1391,9 +1343,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>True</t>
@@ -1405,14 +1355,12 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/a9f696a47ab44c46aaf4f6e4ec3079d4/detail</t>
@@ -1461,9 +1409,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>True</t>
@@ -1475,14 +1421,12 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2540</v>
+        <v>2552</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>https://data.sd.gov.cn/portal/api/e14f04e030db4d81ac84c500d828eb37/detail</t>
@@ -1498,32 +1442,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>菏泽市企业注销信息查询服务</t>
+          <t>市科技成果奖分页查询服务</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>菏泽市企业注销信息查询服务</t>
+          <t>市科技成果奖分页查询服务</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>菏泽市行政审批服务局</t>
+          <t>菏泽市定陶区</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1531,9 +1475,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>True</t>
@@ -1545,17 +1487,15 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4554</v>
+        <v>3073</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/72813d95333f43d3864d77ef4ffb5253/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/07b25aea7b4243fbbdc737415beba10b/detail</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1568,32 +1508,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>菏泽市企业变更信息查询服务</t>
+          <t>餐饮具专项整治监督抽检信息分页查询服务</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>社会民生</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>菏泽市企业变更信息查询服务</t>
+          <t>餐饮具专项整治监督抽检信息分页查询服务</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>菏泽市行政审批服务局</t>
+          <t>菏泽市成武县</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1601,9 +1541,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>True</t>
@@ -1615,17 +1553,15 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3181</v>
+        <v>2574</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/6e5d3fc3cbc0419886d67db23ba45459/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/1443d0be0fec44b7b5aadd796141854b/detail</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1638,7 +1574,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>菏泽市工商开业登记信息查询服务</t>
+          <t>建设用地使用权供应结果信息分页查询服务</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1648,22 +1584,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>菏泽市工商开业登记信息查询服务</t>
+          <t>建设用地使用权供应结果信息分页查询服务</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>菏泽市行政审批服务局</t>
+          <t>菏泽市牡丹区</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1671,9 +1607,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>True</t>
@@ -1685,17 +1619,15 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4638</v>
+        <v>2608</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/f50a5536dd1949da9b3a889e30fd6e8f/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/1f4f17f55aaa41bdb4ebfe0105bf5e51/detail</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1708,17 +1640,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>市科技成果奖分页查询服务</t>
+          <t>建筑业参保统计分页查询服务</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>市科技成果奖分页查询服务</t>
+          <t>建筑业参保统计分页查询服务</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1741,9 +1673,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>True</t>
@@ -1755,17 +1685,15 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3065</v>
+        <v>2291</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/07b25aea7b4243fbbdc737415beba10b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/2c5a6b57ef49468daa1d380ad505a106/detail</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -1778,27 +1706,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>餐饮具专项整治监督抽检信息分页查询服务</t>
+          <t>林业工作任务分配表数据量查询服务</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>社会民生</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>餐饮具专项整治监督抽检信息分页查询服务</t>
+          <t>林业工作任务分配表数据量查询服务</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>菏泽市成武县</t>
+          <t>菏泽市东明县</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1811,9 +1739,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>True</t>
@@ -1825,17 +1751,15 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2572</v>
+        <v>1745</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/1443d0be0fec44b7b5aadd796141854b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/3a129e8746d54c63b0d07697a0f89574/detail</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -1848,27 +1772,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>建设用地使用权供应结果信息分页查询服务</t>
+          <t>商品房预售许可证信息数据量查询服务</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>建设用地使用权供应结果信息分页查询服务</t>
+          <t>商品房预售许可证信息数据量查询服务</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>菏泽市牡丹区</t>
+          <t>菏泽市郓城县</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1881,9 +1805,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>True</t>
@@ -1895,17 +1817,15 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2603</v>
+        <v>2789</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/1f4f17f55aaa41bdb4ebfe0105bf5e51/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5568816bf1f046c785db3c564d6ef3bd/detail</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -1918,27 +1838,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>建筑业参保统计分页查询服务</t>
+          <t>建设用地使用权供应结果信息数据量查询服务</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>市场监督</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>建筑业参保统计分页查询服务</t>
+          <t>建设用地使用权供应结果信息数据量查询服务</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>菏泽市定陶区</t>
+          <t>菏泽市牡丹区</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1951,9 +1871,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>True</t>
@@ -1965,17 +1883,15 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2275</v>
+        <v>757</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2c5a6b57ef49468daa1d380ad505a106/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/638d86096e7f4433ab38e4fea3dce847/detail</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -1988,27 +1904,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>林业工作任务分配表数据量查询服务</t>
+          <t>餐饮具专项整治监督抽检信息数据量查询服务</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>资源环境</t>
+          <t>社会民生</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>林业工作任务分配表数据量查询服务</t>
+          <t>餐饮具专项整治监督抽检信息数据量查询服务</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>菏泽市东明县</t>
+          <t>菏泽市成武县</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2021,9 +1937,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>True</t>
@@ -2035,17 +1949,15 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1741</v>
+        <v>1102</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/3a129e8746d54c63b0d07697a0f89574/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/70c6b03c88744355afdea53e1089fd68/detail</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2058,7 +1970,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>商品房预售许可证信息数据量查询服务</t>
+          <t>建设项目用地预审结果信息分页查询服务</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2068,17 +1980,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>商品房预售许可证信息数据量查询服务</t>
+          <t>建设项目用地预审结果信息分页查询服务</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>菏泽市郓城县</t>
+          <t>菏泽市牡丹区</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2091,9 +2003,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>True</t>
@@ -2105,17 +2015,15 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2778</v>
+        <v>814</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5568816bf1f046c785db3c564d6ef3bd/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7500adab9a4346dcb99451c165280294/detail</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2128,22 +2036,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>建设项目用地预审结果信息分页查询服务</t>
+          <t>食品摊点企业信息数据量查询服务</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>市场监督</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>建设项目用地预审结果信息分页查询服务</t>
+          <t>食品摊点企业信息数据量查询服务</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>菏泽市牡丹区</t>
+          <t>菏泽市成武县</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2161,9 +2069,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>True</t>
@@ -2175,17 +2081,15 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>813</v>
+        <v>217</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7500adab9a4346dcb99451c165280294/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/9b66b33d2610470ebbad198ea99d9250/detail</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2198,27 +2102,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>基准地价和土地分类价格信息分页查询服务</t>
+          <t>市科技成果奖数据量查询服务</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>基准地价和土地分类价格信息分页查询服务</t>
+          <t>市科技成果奖数据量查询服务</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>菏泽市牡丹区</t>
+          <t>菏泽市定陶区</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2231,9 +2135,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>True</t>
@@ -2245,17 +2147,15 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>704</v>
+        <v>193</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/cd22778ab0b2438d94536d61c55321d5/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/a0f8ed3bb3b04cdf997b8a92f54a6391/detail</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2268,27 +2168,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>定陶区公共场所卫生违法查处情况信息数据量查询服务</t>
+          <t>基准地价和土地分类价格信息分页查询服务</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>定陶区公共场所卫生违法查处情况信息数据量查询服务</t>
+          <t>基准地价和土地分类价格信息分页查询服务</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>菏泽市定陶区</t>
+          <t>菏泽市牡丹区</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2301,9 +2201,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>True</t>
@@ -2315,17 +2213,15 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>61</v>
+        <v>709</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d0fb3f3067924a11a7ea1ddd312c11df/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/cd22778ab0b2438d94536d61c55321d5/detail</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2338,22 +2234,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>县道管理信息数据量查询服务</t>
+          <t>定陶区公共场所卫生违法查处情况信息数据量查询服务</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>县道管理信息数据量查询服务</t>
+          <t>定陶区公共场所卫生违法查处情况信息数据量查询服务</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>菏泽市成武县</t>
+          <t>菏泽市定陶区</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2371,9 +2267,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>True</t>
@@ -2385,17 +2279,15 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d1d1f8a961924b7b8cea8655b8dc57d3/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/d0fb3f3067924a11a7ea1ddd312c11df/detail</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2408,27 +2300,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中小学机构代码维护信息分页查询服务</t>
+          <t>县道管理信息数据量查询服务</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>中小学机构代码维护信息分页查询服务</t>
+          <t>县道管理信息数据量查询服务</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>菏泽市定陶区</t>
+          <t>菏泽市成武县</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2441,9 +2333,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>True</t>
@@ -2455,17 +2345,15 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/e78e13ec600b41269bbb389fb154f806/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/d1d1f8a961924b7b8cea8655b8dc57d3/detail</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2478,27 +2366,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>建设用地使用权供应结果信息数据量查询服务</t>
+          <t>中小学机构代码维护信息分页查询服务</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>建设用地使用权供应结果信息数据量查询服务</t>
+          <t>中小学机构代码维护信息分页查询服务</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>菏泽市牡丹区</t>
+          <t>菏泽市定陶区</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2511,9 +2399,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>True</t>
@@ -2525,17 +2411,15 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>752</v>
+        <v>87</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/638d86096e7f4433ab38e4fea3dce847/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/e78e13ec600b41269bbb389fb154f806/detail</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2548,27 +2432,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>餐饮具专项整治监督抽检信息数据量查询服务</t>
+          <t>医疗机构信息一览表分页查询服务</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>社会民生</t>
+          <t>机构团体</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>餐饮具专项整治监督抽检信息数据量查询服务</t>
+          <t>医疗机构信息一览表分页查询服务</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>菏泽市成武县</t>
+          <t>菏泽市东明县</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2581,9 +2465,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>True</t>
@@ -2595,17 +2477,15 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1100</v>
+        <v>2375</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/70c6b03c88744355afdea53e1089fd68/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/2a951b99161540e9979e19ef34059593/detail</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -2618,17 +2498,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>食品摊点企业信息数据量查询服务</t>
+          <t>普通中小学招生范围信息数据量查询服务</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>食品摊点企业信息数据量查询服务</t>
+          <t>普通中小学招生范围信息数据量查询服务</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2651,9 +2531,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>True</t>
@@ -2665,17 +2543,15 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>214</v>
+        <v>64</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/9b66b33d2610470ebbad198ea99d9250/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/237349b513694be2b8da3e0808f2aec2/detail</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -2688,27 +2564,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>市科技成果奖数据量查询服务</t>
+          <t>医疗机构信息一览表分页查询服务</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>机构团体</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>市科技成果奖数据量查询服务</t>
+          <t>医疗机构信息一览表分页查询服务</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>菏泽市定陶区</t>
+          <t>菏泽市东明县</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2721,9 +2597,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>True</t>
@@ -2735,17 +2609,15 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>190</v>
+        <v>2375</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/a0f8ed3bb3b04cdf997b8a92f54a6391/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/2a951b99161540e9979e19ef34059593/detail</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -2758,27 +2630,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>中小学机构代码维护信息数据量查询服务</t>
+          <t>绿色建筑节能备案登记信息数据量查询服务</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>中小学机构代码维护信息数据量查询服务</t>
+          <t>绿色建筑节能备案登记信息数据量查询服务</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>菏泽市定陶区</t>
+          <t>菏泽市成武县</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2791,9 +2663,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>True</t>
@@ -2805,17 +2675,15 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/1a9c9aec4b434893b19da0f4518c66a6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/2b05fbb86f894d6197b608e4141494c0/detail</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -2828,27 +2696,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>普通中小学招生范围信息数据量查询服务</t>
+          <t>医疗机构信息一览表数据量查询服务</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>机构团体</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>普通中小学招生范围信息数据量查询服务</t>
+          <t>医疗机构信息一览表数据量查询服务</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>菏泽市成武县</t>
+          <t>菏泽市东明县</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2861,9 +2729,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>True</t>
@@ -2875,17 +2741,15 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>60</v>
+        <v>2353</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/237349b513694be2b8da3e0808f2aec2/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/2e99ae5473834a4191a20235a6be2b78/detail</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -2898,27 +2762,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>医疗机构信息一览表分页查询服务</t>
+          <t>学校卫生被监管单位信息分页查询服务</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>机构团体</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>医疗机构信息一览表分页查询服务</t>
+          <t>学校卫生被监管单位信息分页查询服务</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>菏泽市东明县</t>
+          <t>菏泽市定陶区</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2931,9 +2795,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>True</t>
@@ -2945,17 +2807,15 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2373</v>
+        <v>1754</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2a951b99161540e9979e19ef34059593/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/543e6a68894f4dbb92e379a30ae00b23/detail</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -2968,7 +2828,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>绿色建筑节能备案登记信息数据量查询服务</t>
+          <t>绿色建筑节能备案登记信息分页查询服务</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2978,7 +2838,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>绿色建筑节能备案登记信息数据量查询服务</t>
+          <t>绿色建筑节能备案登记信息分页查询服务</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3001,9 +2861,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>True</t>
@@ -3015,17 +2873,15 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2b05fbb86f894d6197b608e4141494c0/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/846a8f30fb584020bf6836010b0926ff/detail</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3038,27 +2894,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>医疗机构信息一览表数据量查询服务</t>
+          <t>建设项目用地预审结果信息数据量查询服务</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>机构团体</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>医疗机构信息一览表数据量查询服务</t>
+          <t>建设项目用地预审结果信息数据量查询服务</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>菏泽市东明县</t>
+          <t>菏泽市牡丹区</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2019-01-09</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3071,9 +2927,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>True</t>
@@ -3085,17 +2939,15 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2351</v>
+        <v>19</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/2e99ae5473834a4191a20235a6be2b78/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/89b2d849338d48eda1719c9ef03935ba/detail</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -3108,7 +2960,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>基准地价和土地分类价格信息数据量查询服务</t>
+          <t>商品房预售许可证信息分页查询服务</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3118,17 +2970,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>基准地价和土地分类价格信息数据量查询服务</t>
+          <t>商品房预售许可证信息分页查询服务</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>菏泽市牡丹区</t>
+          <t>菏泽市郓城县</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3141,9 +2993,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>True</t>
@@ -3155,17 +3005,15 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/b5af0517761f46659a9be516a0a520a5/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/8ac460eedd154d54bf807c3a57d63967/detail</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -3178,17 +3026,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>学校卫生被监管单位信息数据量查询服务</t>
+          <t>定陶区公共场所卫生违法查处情况信息分页查询服务</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>学校卫生被监管单位信息数据量查询服务</t>
+          <t>定陶区公共场所卫生违法查处情况信息分页查询服务</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3198,7 +3046,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3211,9 +3059,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>True</t>
@@ -3225,17 +3071,15 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1786</v>
+        <v>61</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/cc5f9e75f2da4a75bdab959566e0d5aa/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/adc03e7c3e0d40f2a39a388b0b91d76a/detail</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -3248,7 +3092,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>守合同重信用企业信息分页查询服务</t>
+          <t>守合同重信用企业信息数据量查询服务</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3258,7 +3102,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>守合同重信用企业信息分页查询服务</t>
+          <t>守合同重信用企业信息数据量查询服务</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3281,9 +3125,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>True</t>
@@ -3295,17 +3137,15 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/cef940df60894589975421e577f38f4b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b37b526a728f41dc900aaea582dcb714/detail</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -3318,27 +3158,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>定陶区公共场所卫生违法查处情况信息分页查询服务</t>
+          <t>基准地价和土地分类价格信息数据量查询服务</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>定陶区公共场所卫生违法查处情况信息分页查询服务</t>
+          <t>基准地价和土地分类价格信息数据量查询服务</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>菏泽市定陶区</t>
+          <t>菏泽市牡丹区</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3351,9 +3191,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>True</t>
@@ -3365,17 +3203,15 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/adc03e7c3e0d40f2a39a388b0b91d76a/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b5af0517761f46659a9be516a0a520a5/detail</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -3388,27 +3224,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>守合同重信用企业信息数据量查询服务</t>
+          <t>学校卫生被监管单位信息数据量查询服务</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>安全监管</t>
+          <t>教育科技</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>守合同重信用企业信息数据量查询服务</t>
+          <t>学校卫生被监管单位信息数据量查询服务</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>菏泽市成武县</t>
+          <t>菏泽市定陶区</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3421,9 +3257,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>True</t>
@@ -3435,17 +3269,15 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>22</v>
+        <v>1788</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/b37b526a728f41dc900aaea582dcb714/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/cc5f9e75f2da4a75bdab959566e0d5aa/detail</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -3458,17 +3290,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>绿色建筑节能备案登记信息分页查询服务</t>
+          <t>守合同重信用企业信息分页查询服务</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>资源环境</t>
+          <t>安全监管</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>绿色建筑节能备案登记信息分页查询服务</t>
+          <t>守合同重信用企业信息分页查询服务</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3491,9 +3323,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>True</t>
@@ -3505,17 +3335,15 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/846a8f30fb584020bf6836010b0926ff/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/cef940df60894589975421e577f38f4b/detail</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -3528,7 +3356,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>建设项目用地预审结果信息数据量查询服务</t>
+          <t>旱情及抗旱统计表分页查询服务</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3538,17 +3366,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>建设项目用地预审结果信息数据量查询服务</t>
+          <t>旱情及抗旱统计表分页查询服务</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>菏泽市牡丹区</t>
+          <t>菏泽市定陶区</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3561,9 +3389,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>True</t>
@@ -3575,17 +3401,15 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/89b2d849338d48eda1719c9ef03935ba/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/0194de7f9c78420cb283286b314d0c42/detail</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -3598,7 +3422,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>商品房预售许可证信息分页查询服务</t>
+          <t>县道管理信息分页查询服务</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3608,12 +3432,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>商品房预售许可证信息分页查询服务</t>
+          <t>县道管理信息分页查询服务</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>菏泽市郓城县</t>
+          <t>菏泽市成武县</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3631,9 +3455,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>True</t>
@@ -3645,17 +3467,15 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/8ac460eedd154d54bf807c3a57d63967/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/0aa68d6c2896437983947755716e42ec/detail</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -3668,7 +3488,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>学校卫生被监管单位信息分页查询服务</t>
+          <t>普通中小学招生范围信息分页查询服务</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3678,17 +3498,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>学校卫生被监管单位信息分页查询服务</t>
+          <t>普通中小学招生范围信息分页查询服务</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>菏泽市定陶区</t>
+          <t>菏泽市成武县</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3701,9 +3521,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>True</t>
@@ -3715,17 +3533,15 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1753</v>
+        <v>58</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/543e6a68894f4dbb92e379a30ae00b23/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/1a01d9851cd6476eb73fedbfc3b2e812/detail</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -3738,7 +3554,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>旱情及抗旱统计表数据量查询服务</t>
+          <t>定陶区社区戒毒社区康复地址及联系电话信息数据量查询服务</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3748,7 +3564,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>旱情及抗旱统计表数据量查询服务</t>
+          <t>定陶区社区戒毒社区康复地址及联系电话信息数据量查询服务</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3758,7 +3574,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3771,9 +3587,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>True</t>
@@ -3785,17 +3599,15 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/da3d24239fb84647b2eaf1a1ad5c3821/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7144d1ae63ac42eb97d60627e35c0074/detail</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -3808,27 +3620,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>食品摊点企业信息分页查询服务</t>
+          <t>定陶区社区戒毒社区康复地址及联系电话信息分页查询服务</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>食品摊点企业信息分页查询服务</t>
+          <t>定陶区社区戒毒社区康复地址及联系电话信息分页查询服务</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>菏泽市成武县</t>
+          <t>菏泽市定陶区</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3841,9 +3653,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>True</t>
@@ -3855,17 +3665,15 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/e2a21a51ce1c4d97aca9721f81d6dd41/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/84745e2cb0704f589f5ca6dad886c1c6/detail</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -3878,27 +3686,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>建筑业参保统计数据量查询服务</t>
+          <t>林业工作任务分配表分页查询服务</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>社保就业</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>建筑业参保统计数据量查询服务</t>
+          <t>林业工作任务分配表分页查询服务</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>菏泽市定陶区</t>
+          <t>菏泽市东明县</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3911,9 +3719,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>True</t>
@@ -3925,17 +3731,15 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/f83f384fa2994946aaeadcc336602f84/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/cbb23ccc59924474b53866d675602acd/detail</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
@@ -3948,27 +3752,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>林业工作任务分配表分页查询服务</t>
+          <t>旱情及抗旱统计表数据量查询服务</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>资源环境</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>林业工作任务分配表分页查询服务</t>
+          <t>旱情及抗旱统计表数据量查询服务</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>菏泽市东明县</t>
+          <t>菏泽市定陶区</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3981,9 +3785,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>True</t>
@@ -3995,17 +3797,15 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/cbb23ccc59924474b53866d675602acd/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/da3d24239fb84647b2eaf1a1ad5c3821/detail</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -4018,27 +3818,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>定陶区社区戒毒社区康复地址及联系电话信息数据量查询服务</t>
+          <t>食品摊点企业信息分页查询服务</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>市场监督</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>定陶区社区戒毒社区康复地址及联系电话信息数据量查询服务</t>
+          <t>食品摊点企业信息分页查询服务</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>菏泽市定陶区</t>
+          <t>菏泽市成武县</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4051,9 +3851,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>True</t>
@@ -4065,17 +3863,15 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7144d1ae63ac42eb97d60627e35c0074/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/e2a21a51ce1c4d97aca9721f81d6dd41/detail</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -4088,17 +3884,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>定陶区社区戒毒社区康复地址及联系电话信息分页查询服务</t>
+          <t>建筑业参保统计数据量查询服务</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>社保就业</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>定陶区社区戒毒社区康复地址及联系电话信息分页查询服务</t>
+          <t>建筑业参保统计数据量查询服务</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4108,7 +3904,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4121,9 +3917,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>True</t>
@@ -4135,17 +3929,15 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/84745e2cb0704f589f5ca6dad886c1c6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/f83f384fa2994946aaeadcc336602f84/detail</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
@@ -4158,27 +3950,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>旱情及抗旱统计表分页查询服务</t>
+          <t>菏泽市基层医疗机构补充药品遴选确定汇总表信息分页查询服务</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>旱情及抗旱统计表分页查询服务</t>
+          <t>菏泽市基层医疗机构补充药品遴选确定汇总表信息分页查询服务</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>菏泽市定陶区</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4191,9 +3983,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>True</t>
@@ -4205,17 +3995,15 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/0194de7f9c78420cb283286b314d0c42/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/3d487ad8ecad4597b18a683068aed322/detail</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -4228,7 +4016,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>县道管理信息分页查询服务</t>
+          <t>生鲜乳运输车信息分页查询服务</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4238,17 +4026,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>县道管理信息分页查询服务</t>
+          <t>生鲜乳运输车信息分页查询服务</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>菏泽市成武县</t>
+          <t>菏泽市畜牧服务中心</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4261,9 +4049,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>True</t>
@@ -4275,17 +4061,15 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/0aa68d6c2896437983947755716e42ec/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/47ffb829020a407e83c3d3fa9ee6f09f/detail</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -4298,22 +4082,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>普通中小学招生范围信息分页查询服务</t>
+          <t>菏泽市结核病定点医院分页查询服务</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>教育科技</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>普通中小学招生范围信息分页查询服务</t>
+          <t>菏泽市结核病定点医院分页查询服务</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>菏泽市成武县</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4331,9 +4115,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>True</t>
@@ -4345,17 +4127,15 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/1a01d9851cd6476eb73fedbfc3b2e812/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/508692348dcc428e8a9a54078c5207d9/detail</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -4368,27 +4148,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>菏泽市基层医疗机构补充药品遴选确定汇总表信息分页查询服务</t>
+          <t>山东省农机购置补贴机具补贴额一览表信息数据量查询服务</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>市场监督</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>菏泽市基层医疗机构补充药品遴选确定汇总表信息分页查询服务</t>
+          <t>山东省农机购置补贴机具补贴额一览表信息数据量查询服务</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市农业机械服务中心</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4401,9 +4181,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>True</t>
@@ -4415,17 +4193,15 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/3d487ad8ecad4597b18a683068aed322/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5595b1298f5a4ceebc616a5dfcad6a9e/detail</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -4438,22 +4214,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>生鲜乳运输车信息分页查询服务</t>
+          <t>菏泽市艾滋病自愿免费咨询检测点信息数据量查询服务</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>生鲜乳运输车信息分页查询服务</t>
+          <t>菏泽市艾滋病自愿免费咨询检测点信息数据量查询服务</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>菏泽市畜牧服务中心</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4471,9 +4247,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>True</t>
@@ -4485,17 +4259,15 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/47ffb829020a407e83c3d3fa9ee6f09f/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/577ee7d03dea454a9e084920759f69d3/detail</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -4508,17 +4280,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>菏泽市结核病定点医院分页查询服务</t>
+          <t>菏泽市中心血站常用血液及价格表信息数据量查询服务</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>市场监督</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>菏泽市结核病定点医院分页查询服务</t>
+          <t>菏泽市中心血站常用血液及价格表信息数据量查询服务</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4541,9 +4313,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>True</t>
@@ -4555,17 +4325,15 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/508692348dcc428e8a9a54078c5207d9/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/57f856a414db4930970ea5ead9063290/detail</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -4578,27 +4346,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>山东省农机购置补贴机具补贴额一览表信息数据量查询服务</t>
+          <t>饲料生产企业信息分页查询服务</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>社会民生</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>山东省农机购置补贴机具补贴额一览表信息数据量查询服务</t>
+          <t>饲料生产企业信息分页查询服务</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>菏泽市农业机械服务中心</t>
+          <t>菏泽市畜牧服务中心</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4611,9 +4379,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>True</t>
@@ -4625,17 +4391,15 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5595b1298f5a4ceebc616a5dfcad6a9e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/6e3e489ff8954c26b3f7d8511eb82404/detail</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -4648,7 +4412,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>菏泽市艾滋病自愿免费咨询检测点信息数据量查询服务</t>
+          <t>菏泽市区急救指挥中心急救站信息数据量查询服务</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4658,7 +4422,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>菏泽市艾滋病自愿免费咨询检测点信息数据量查询服务</t>
+          <t>菏泽市区急救指挥中心急救站信息数据量查询服务</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4681,9 +4445,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>True</t>
@@ -4695,17 +4457,15 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/577ee7d03dea454a9e084920759f69d3/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/736bc06bea43436f95652aefe71617c4/detail</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -4718,7 +4478,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>菏泽市中心血站常用血液及价格表信息数据量查询服务</t>
+          <t>兽药生产企业汇总信息数据量查询服务</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4728,12 +4488,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>菏泽市中心血站常用血液及价格表信息数据量查询服务</t>
+          <t>兽药生产企业汇总信息数据量查询服务</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市畜牧服务中心</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4751,9 +4511,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>True</t>
@@ -4765,17 +4523,15 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/57f856a414db4930970ea5ead9063290/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/757fecee8c554f2c8f145908cadd76a1/detail</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -4788,27 +4544,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>菏泽市二级以上医疗机构已认定医院等级情况信息数据量查询服务</t>
+          <t>全市旅游景点管理信息分页查询服务</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>菏泽市二级以上医疗机构已认定医院等级情况信息数据量查询服务</t>
+          <t>全市旅游景点管理信息分页查询服务</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市文化和旅游局</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4821,9 +4577,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>True</t>
@@ -4835,17 +4589,15 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>40</v>
+        <v>168</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/dc50778a4dd44a18a15757b92c6f7d37/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7aa9c65cc3e24965b809fd063a9ea234/detail</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -4858,7 +4610,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>生鲜乳运输车信息数据量查询服务</t>
+          <t>星级饭店统计表数据量查询服务</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4868,12 +4620,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>生鲜乳运输车信息数据量查询服务</t>
+          <t>星级饭店统计表数据量查询服务</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>菏泽市畜牧服务中心</t>
+          <t>菏泽市文化和旅游局</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4891,9 +4643,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>True</t>
@@ -4905,17 +4655,15 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>109</v>
+        <v>5015</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/e5041c887c604264bae3e172b9884f5e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/9a5ce006d3e84a4c8f3ced7f2d8dc972/detail</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
@@ -4928,7 +4676,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>菏泽市120急救指挥中心所获荣誉信息数据量查询服务</t>
+          <t>菏泽市120急救指挥中心所获荣誉信息分页查询服务</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4938,7 +4686,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>菏泽市120急救指挥中心所获荣誉信息数据量查询服务</t>
+          <t>菏泽市120急救指挥中心所获荣誉信息分页查询服务</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4961,9 +4709,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>True</t>
@@ -4975,17 +4721,15 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/ec0008b21c3b46d1813313275c65501d/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/9bf58a13fee84102ace809ea7efedd6b/detail</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -4998,27 +4742,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>饲料生产企业信息分页查询服务</t>
+          <t>菏泽市级病残儿医学鉴定神经科清单信息数据量查询服务</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>社会民生</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>饲料生产企业信息分页查询服务</t>
+          <t>菏泽市级病残儿医学鉴定神经科清单信息数据量查询服务</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>菏泽市畜牧服务中心</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2019-03-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5031,9 +4775,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>True</t>
@@ -5045,17 +4787,15 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/6e3e489ff8954c26b3f7d8511eb82404/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/d07be95ac4e04bde8879248f7d9a2e89/detail</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -5068,7 +4808,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>菏泽市区急救指挥中心急救站信息数据量查询服务</t>
+          <t>菏泽市二级以上医疗机构已认定医院等级情况信息数据量查询服务</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5078,7 +4818,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>菏泽市区急救指挥中心急救站信息数据量查询服务</t>
+          <t>菏泽市二级以上医疗机构已认定医院等级情况信息数据量查询服务</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5101,9 +4841,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>True</t>
@@ -5115,17 +4853,15 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/736bc06bea43436f95652aefe71617c4/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/dc50778a4dd44a18a15757b92c6f7d37/detail</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
@@ -5138,17 +4874,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>兽药生产企业汇总信息数据量查询服务</t>
+          <t>生鲜乳运输车信息数据量查询服务</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>兽药生产企业汇总信息数据量查询服务</t>
+          <t>生鲜乳运输车信息数据量查询服务</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5171,9 +4907,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>True</t>
@@ -5185,17 +4919,15 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/757fecee8c554f2c8f145908cadd76a1/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/e5041c887c604264bae3e172b9884f5e/detail</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -5208,27 +4940,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>全市旅游景点管理信息分页查询服务</t>
+          <t>菏泽市120急救指挥中心所获荣誉信息数据量查询服务</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>全市旅游景点管理信息分页查询服务</t>
+          <t>菏泽市120急救指挥中心所获荣誉信息数据量查询服务</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>菏泽市文化和旅游局</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5241,9 +4973,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>True</t>
@@ -5255,17 +4985,15 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7aa9c65cc3e24965b809fd063a9ea234/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/ec0008b21c3b46d1813313275c65501d/detail</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -5278,27 +5006,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>菏泽市级病残儿医学鉴定神经科清单信息数据量查询服务</t>
+          <t>菏泽市十三五生态环境保护规划主要指标信息数据量查询服务</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>菏泽市级病残儿医学鉴定神经科清单信息数据量查询服务</t>
+          <t>菏泽市十三五生态环境保护规划主要指标信息数据量查询服务</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市生态环境局</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2019-03-05</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5311,9 +5039,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>True</t>
@@ -5325,17 +5051,15 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>22</v>
+        <v>4593</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
       </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d07be95ac4e04bde8879248f7d9a2e89/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/07ec2aee7fa94154adf98f8bf925d1a4/detail</t>
         </is>
       </c>
       <c r="P70" t="inlineStr"/>
@@ -5348,7 +5072,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>星级饭店统计表数据量查询服务</t>
+          <t>菏泽市国资委文件管理分页查询服务</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5358,17 +5082,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>星级饭店统计表数据量查询服务</t>
+          <t>菏泽市国资委文件管理分页查询服务</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>菏泽市文化和旅游局</t>
+          <t>菏泽市人民政府国有资产监督管理委员会</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2019-03-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5381,9 +5105,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>True</t>
@@ -5395,17 +5117,15 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4884</v>
+        <v>12277</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/9a5ce006d3e84a4c8f3ced7f2d8dc972/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/249d57ae11984aa09c92779a4b4db924/detail</t>
         </is>
       </c>
       <c r="P71" t="inlineStr"/>
@@ -5418,27 +5138,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>菏泽市120急救指挥中心所获荣誉信息分页查询服务</t>
+          <t>菏泽市国资委文件管理数据量查询服务</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>菏泽市120急救指挥中心所获荣誉信息分页查询服务</t>
+          <t>菏泽市国资委文件管理数据量查询服务</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市人民政府国有资产监督管理委员会</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2019-03-05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5451,9 +5171,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>True</t>
@@ -5465,17 +5183,15 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>115</v>
+        <v>16887</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/9bf58a13fee84102ace809ea7efedd6b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/42379bcc0e1046dcac53e258ec8acaec/detail</t>
         </is>
       </c>
       <c r="P72" t="inlineStr"/>
@@ -5488,22 +5204,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>菏泽市十三五生态环境保护规划主要指标信息数据量查询服务</t>
+          <t>菏泽市结核病定点医院数据量查询服务</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>资源环境</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>菏泽市十三五生态环境保护规划主要指标信息数据量查询服务</t>
+          <t>菏泽市结核病定点医院数据量查询服务</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>菏泽市生态环境局</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5521,9 +5237,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>True</t>
@@ -5535,17 +5249,15 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>4460</v>
+        <v>41</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/07ec2aee7fa94154adf98f8bf925d1a4/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/6049002f40664eadb2b91ea1eda84463/detail</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -5558,22 +5270,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>菏泽市母婴保健机构信息分页查询服务</t>
+          <t>农机购置补贴信息数据量查询服务</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>农业农村</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>菏泽市母婴保健机构信息分页查询服务</t>
+          <t>农机购置补贴信息数据量查询服务</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市农业机械服务中心</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5591,9 +5303,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>True</t>
@@ -5605,17 +5315,15 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7985916ad9584e4292d0dbcaac85be6e/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/67cb6ea0012b45989601061e9bc39708/detail</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -5628,22 +5336,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>兽药生产企业汇总信息分页查询服务</t>
+          <t>菏泽市母婴保健机构信息分页查询服务</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>兽药生产企业汇总信息分页查询服务</t>
+          <t>菏泽市母婴保健机构信息分页查询服务</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>菏泽市畜牧服务中心</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5661,9 +5369,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>True</t>
@@ -5675,17 +5381,15 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>168</v>
+        <v>47</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7b172f25ea9f46459cf5baca6a39913b/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7985916ad9584e4292d0dbcaac85be6e/detail</t>
         </is>
       </c>
       <c r="P75" t="inlineStr"/>
@@ -5698,22 +5402,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>菏泽市母婴保健机构信息数据量查询服务</t>
+          <t>兽药生产企业汇总信息分页查询服务</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>市场监督</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>菏泽市母婴保健机构信息数据量查询服务</t>
+          <t>兽药生产企业汇总信息分页查询服务</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市畜牧服务中心</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5731,9 +5435,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>True</t>
@@ -5745,17 +5447,15 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>45</v>
+        <v>176</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/7e1ab39c05f44e53b36f4dd1fd39345c/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7b172f25ea9f46459cf5baca6a39913b/detail</t>
         </is>
       </c>
       <c r="P76" t="inlineStr"/>
@@ -5768,7 +5468,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>菏泽市临时救助数据统计表信息分页查询服务</t>
+          <t>菏泽市母婴保健机构信息数据量查询服务</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5778,17 +5478,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>菏泽市临时救助数据统计表信息分页查询服务</t>
+          <t>菏泽市母婴保健机构信息数据量查询服务</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>菏泽市民政局</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5801,9 +5501,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>True</t>
@@ -5815,17 +5513,15 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3616</v>
+        <v>48</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
       </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/853e8b24a0c64bd4bf6e2a0170fbc0f7/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/7e1ab39c05f44e53b36f4dd1fd39345c/detail</t>
         </is>
       </c>
       <c r="P77" t="inlineStr"/>
@@ -5838,27 +5534,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>饲料生产企业信息数据量查询服务</t>
+          <t>菏泽市临时救助数据统计表信息分页查询服务</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>社会民生</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>饲料生产企业信息数据量查询服务</t>
+          <t>菏泽市临时救助数据统计表信息分页查询服务</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>菏泽市畜牧服务中心</t>
+          <t>菏泽市民政局</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5871,9 +5567,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>True</t>
@@ -5885,17 +5579,15 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>119</v>
+        <v>3752</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/8dfea6c6b38d4416a85fafe99a3cedbf/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/853e8b24a0c64bd4bf6e2a0170fbc0f7/detail</t>
         </is>
       </c>
       <c r="P78" t="inlineStr"/>
@@ -5908,22 +5600,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>菏泽市中心血站常用血液及价格表信息分页查询服务</t>
+          <t>饲料生产企业信息数据量查询服务</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>市场监督</t>
+          <t>社会民生</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>菏泽市中心血站常用血液及价格表信息分页查询服务</t>
+          <t>饲料生产企业信息数据量查询服务</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市畜牧服务中心</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5941,9 +5633,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>True</t>
@@ -5955,17 +5645,15 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/c10174389c2b45f698a9293e3b8080c6/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/8dfea6c6b38d4416a85fafe99a3cedbf/detail</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -5978,17 +5666,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>星级饭店统计表分页查询服务</t>
+          <t>全市工业旅游示范点名录分页查询服务</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>地理空间</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>星级饭店统计表分页查询服务</t>
+          <t>全市工业旅游示范点名录分页查询服务</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6011,9 +5699,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>True</t>
@@ -6025,17 +5711,15 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4523</v>
+        <v>44</v>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/c371e686c2f44cca9840dee7bd4ffb52/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/906f62c005d54001a536ea465531f2dc/detail</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
@@ -6048,22 +5732,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>全市工业旅游示范点名录数据量查询服务</t>
+          <t>菏泽市艾滋病自愿免费咨询检测点信息分页查询服务</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>地理空间</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>全市工业旅游示范点名录数据量查询服务</t>
+          <t>菏泽市艾滋病自愿免费咨询检测点信息分页查询服务</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>菏泽市文化和旅游局</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6081,9 +5765,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>True</t>
@@ -6095,17 +5777,15 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/e9459b5aa62f4ab588ec62eef6933563/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b042842406f94371aac83ba63e3e37f5/detail</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
@@ -6118,27 +5798,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>水库移民后期扶持规划数据量查询服务</t>
+          <t>全市工业旅游示范点名录数据量查询服务</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>地理空间</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>水库移民后期扶持规划数据量查询服务</t>
+          <t>全市工业旅游示范点名录数据量查询服务</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>菏泽市水务局</t>
+          <t>菏泽市文化和旅游局</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6151,9 +5831,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>True</t>
@@ -6165,17 +5843,15 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3660</v>
+        <v>38</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/ef8322af3cba427bad6d96924e294ed5/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/e9459b5aa62f4ab588ec62eef6933563/detail</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -6188,27 +5864,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>菏泽市基层医疗机构补充药品遴选确定汇总表信息数据量查询服务</t>
+          <t>水库移民后期扶持规划数据量查询服务</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>菏泽市基层医疗机构补充药品遴选确定汇总表信息数据量查询服务</t>
+          <t>水库移民后期扶持规划数据量查询服务</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市水务局</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6221,9 +5897,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>True</t>
@@ -6235,17 +5909,15 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>123</v>
+        <v>3798</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/fa6f2d10f271481f812651b352fea3c7/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/ef8322af3cba427bad6d96924e294ed5/detail</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -6258,27 +5930,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>菏泽市国资委文件管理分页查询服务</t>
+          <t>菏泽市基层医疗机构补充药品遴选确定汇总表信息数据量查询服务</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>菏泽市国资委文件管理分页查询服务</t>
+          <t>菏泽市基层医疗机构补充药品遴选确定汇总表信息数据量查询服务</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>菏泽市人民政府国有资产监督管理委员会</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2019-03-05</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6291,9 +5963,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>True</t>
@@ -6305,17 +5975,15 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>12144</v>
+        <v>125</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/249d57ae11984aa09c92779a4b4db924/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/fa6f2d10f271481f812651b352fea3c7/detail</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -6328,27 +5996,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>菏泽市国资委文件管理数据量查询服务</t>
+          <t>菏泽市中心血站常用血液及价格表信息分页查询服务</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>市场监督</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>菏泽市国资委文件管理数据量查询服务</t>
+          <t>菏泽市中心血站常用血液及价格表信息分页查询服务</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>菏泽市人民政府国有资产监督管理委员会</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2019-03-05</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6361,9 +6029,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>True</t>
@@ -6375,17 +6041,15 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>16755</v>
+        <v>87</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/42379bcc0e1046dcac53e258ec8acaec/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/c10174389c2b45f698a9293e3b8080c6/detail</t>
         </is>
       </c>
       <c r="P85" t="inlineStr"/>
@@ -6398,22 +6062,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>菏泽市艾滋病自愿免费咨询检测点信息分页查询服务</t>
+          <t>星级饭店统计表分页查询服务</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>菏泽市艾滋病自愿免费咨询检测点信息分页查询服务</t>
+          <t>星级饭店统计表分页查询服务</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市文化和旅游局</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6431,9 +6095,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>True</t>
@@ -6445,17 +6107,15 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>30</v>
+        <v>4655</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/b042842406f94371aac83ba63e3e37f5/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/c371e686c2f44cca9840dee7bd4ffb52/detail</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -6468,27 +6128,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>全市工业旅游示范点名录分页查询服务</t>
+          <t>菏泽市临时救助数据统计表信息数据量查询服务</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>地理空间</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>全市工业旅游示范点名录分页查询服务</t>
+          <t>菏泽市临时救助数据统计表信息数据量查询服务</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>菏泽市文化和旅游局</t>
+          <t>菏泽市民政局</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,9 +6161,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>True</t>
@@ -6515,17 +6173,15 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>42</v>
+        <v>3679</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/906f62c005d54001a536ea465531f2dc/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/03f562dd0898440daffef4c89906457e/detail</t>
         </is>
       </c>
       <c r="P87" t="inlineStr"/>
@@ -6538,7 +6194,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>菏泽市结核病定点医院数据量查询服务</t>
+          <t>菏泽市级病残儿医学鉴定神经科清单信息分页查询服务</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6548,7 +6204,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>菏泽市结核病定点医院数据量查询服务</t>
+          <t>菏泽市级病残儿医学鉴定神经科清单信息分页查询服务</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6558,7 +6214,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2019-03-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6571,9 +6227,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>True</t>
@@ -6585,17 +6239,15 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
       </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/6049002f40664eadb2b91ea1eda84463/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/29069a21de9146eeae78e96e7dc1bf3e/detail</t>
         </is>
       </c>
       <c r="P88" t="inlineStr"/>
@@ -6608,22 +6260,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>农机购置补贴信息数据量查询服务</t>
+          <t>菏泽市二级以上医疗机构已认定医院等级情况信息分页查询服务</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>农业农村</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>农机购置补贴信息数据量查询服务</t>
+          <t>菏泽市二级以上医疗机构已认定医院等级情况信息分页查询服务</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>菏泽市农业机械服务中心</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6641,9 +6293,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>True</t>
@@ -6655,17 +6305,15 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>151</v>
+        <v>29</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/67cb6ea0012b45989601061e9bc39708/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/49a13aa29c1345b1a691b84aab0a0ed1/detail</t>
         </is>
       </c>
       <c r="P89" t="inlineStr"/>
@@ -6678,7 +6326,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>菏泽市疾病预防控制机构信息一览表信息分页查询服务</t>
+          <t>菏泽市国家免费提供避孕药具发放服务点信息数据量查询服务</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6688,7 +6336,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>菏泽市疾病预防控制机构信息一览表信息分页查询服务</t>
+          <t>菏泽市国家免费提供避孕药具发放服务点信息数据量查询服务</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6711,9 +6359,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>True</t>
@@ -6725,17 +6371,15 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1800</v>
+        <v>122</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/f750de9d283c4b619855dda0762597c7/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/5a04524f9bab49c6bc3c1f6e5ebb9771/detail</t>
         </is>
       </c>
       <c r="P90" t="inlineStr"/>
@@ -6748,22 +6392,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>农机购置补贴信息分页查询服务</t>
+          <t>菏泽市供销社年度安全生产工作先进个人名单信息分页查询服务</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>农业农村</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>农机购置补贴信息分页查询服务</t>
+          <t>菏泽市供销社年度安全生产工作先进个人名单信息分页查询服务</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>菏泽市农业机械服务中心</t>
+          <t>菏泽市供销合作社</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6781,9 +6425,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>True</t>
@@ -6795,17 +6437,15 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
       </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/b85f4e1c6dc041aa95063b31c0cd62f4/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/612f3697875a459dadcc0e6f08b52371/detail</t>
         </is>
       </c>
       <c r="P91" t="inlineStr"/>
@@ -6818,22 +6458,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>菏泽市十三五生态环境保护规划主要指标信息分页查询服务</t>
+          <t>菏泽市中心血站采血站点信息数据量查询服务</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>资源环境</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>菏泽市十三五生态环境保护规划主要指标信息分页查询服务</t>
+          <t>菏泽市中心血站采血站点信息数据量查询服务</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>菏泽市生态环境局</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6851,9 +6491,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>True</t>
@@ -6865,17 +6503,15 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>4645</v>
+        <v>61</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/bd162fd33a3f47d38ca0681e6179dbeb/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/650b8b74c5014f44b2eddf22567a8329/detail</t>
         </is>
       </c>
       <c r="P92" t="inlineStr"/>
@@ -6888,27 +6524,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>菏泽市国家免费提供避孕药具发放服务点信息分页查询服务</t>
+          <t>水库移民后期扶持规划分页查询服务</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>菏泽市国家免费提供避孕药具发放服务点信息分页查询服务</t>
+          <t>水库移民后期扶持规划分页查询服务</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市水务局</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6921,9 +6557,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>True</t>
@@ -6935,17 +6569,15 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>136</v>
+        <v>3822</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/cba29dcbcfa74600b68be280c27017cc/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/6dd372a841934faa929c6f4c7bd54e06/detail</t>
         </is>
       </c>
       <c r="P93" t="inlineStr"/>
@@ -6958,27 +6590,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>全市旅游景点管理信息数据量查询服务</t>
+          <t>菏泽市疾病预防控制机构信息一览表信息数据量查询服务</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>全市旅游景点管理信息数据量查询服务</t>
+          <t>菏泽市疾病预防控制机构信息一览表信息数据量查询服务</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>菏泽市文化和旅游局</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6991,9 +6623,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>True</t>
@@ -7005,17 +6635,15 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>158</v>
+        <v>2048</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d1ffa55e45db499ab9af497bf53e80e0/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/8c90e6707f314c5786c4a698f87b449a/detail</t>
         </is>
       </c>
       <c r="P94" t="inlineStr"/>
@@ -7028,22 +6656,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>菏泽市中心血站采血站点信息分页查询服务</t>
+          <t>菏泽市供销社年度安全生产工作先进个人名单信息数据量查询服务</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>菏泽市中心血站采血站点信息分页查询服务</t>
+          <t>菏泽市供销社年度安全生产工作先进个人名单信息数据量查询服务</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市供销合作社</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7061,9 +6689,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>True</t>
@@ -7075,17 +6701,15 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>61</v>
+        <v>134</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/d7f8819a676b4f16b87e986bb7a82411/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/a5433bb69b754604938662c82b4d89d2/detail</t>
         </is>
       </c>
       <c r="P95" t="inlineStr"/>
@@ -7098,7 +6722,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>菏泽市中心血站采血站点信息数据量查询服务</t>
+          <t>菏泽市区急救指挥中心急救站信息分页查询服务</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7108,7 +6732,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>菏泽市中心血站采血站点信息数据量查询服务</t>
+          <t>菏泽市区急救指挥中心急救站信息分页查询服务</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7131,9 +6755,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>True</t>
@@ -7145,17 +6767,15 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
       </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/650b8b74c5014f44b2eddf22567a8329/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/a7ca6c91cc0d40038dea0609c78342de/detail</t>
         </is>
       </c>
       <c r="P96" t="inlineStr"/>
@@ -7168,27 +6788,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>水库移民后期扶持规划分页查询服务</t>
+          <t>农机购置补贴信息分页查询服务</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>农业农村</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>水库移民后期扶持规划分页查询服务</t>
+          <t>农机购置补贴信息分页查询服务</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>菏泽市水务局</t>
+          <t>菏泽市农业机械服务中心</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7201,9 +6821,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>True</t>
@@ -7215,17 +6833,15 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3687</v>
+        <v>165</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
       </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/6dd372a841934faa929c6f4c7bd54e06/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/b85f4e1c6dc041aa95063b31c0cd62f4/detail</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -7238,22 +6854,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>菏泽市二级以上医疗机构已认定医院等级情况信息分页查询服务</t>
+          <t>菏泽市十三五生态环境保护规划主要指标信息分页查询服务</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>资源环境</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>菏泽市二级以上医疗机构已认定医院等级情况信息分页查询服务</t>
+          <t>菏泽市十三五生态环境保护规划主要指标信息分页查询服务</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市生态环境局</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7271,9 +6887,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>True</t>
@@ -7285,17 +6899,15 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>28</v>
+        <v>4778</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/49a13aa29c1345b1a691b84aab0a0ed1/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/bd162fd33a3f47d38ca0681e6179dbeb/detail</t>
         </is>
       </c>
       <c r="P98" t="inlineStr"/>
@@ -7308,22 +6920,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>菏泽市供销社年度安全生产工作先进个人名单信息数据量查询服务</t>
+          <t>菏泽市国家免费提供避孕药具发放服务点信息分页查询服务</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>卫生健康</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>菏泽市供销社年度安全生产工作先进个人名单信息数据量查询服务</t>
+          <t>菏泽市国家免费提供避孕药具发放服务点信息分页查询服务</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>菏泽市供销合作社</t>
+          <t>菏泽市卫生健康委员会</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7341,9 +6953,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>True</t>
@@ -7355,17 +6965,15 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/a5433bb69b754604938662c82b4d89d2/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/cba29dcbcfa74600b68be280c27017cc/detail</t>
         </is>
       </c>
       <c r="P99" t="inlineStr"/>
@@ -7378,27 +6986,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>菏泽市区急救指挥中心急救站信息分页查询服务</t>
+          <t>全市旅游景点管理信息数据量查询服务</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>卫生健康</t>
+          <t>综合政务</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>菏泽市区急救指挥中心急救站信息分页查询服务</t>
+          <t>全市旅游景点管理信息数据量查询服务</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>菏泽市卫生健康委员会</t>
+          <t>菏泽市文化和旅游局</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7411,9 +7019,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>True</t>
@@ -7425,17 +7031,15 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
       </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/a7ca6c91cc0d40038dea0609c78342de/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/d1ffa55e45db499ab9af497bf53e80e0/detail</t>
         </is>
       </c>
       <c r="P100" t="inlineStr"/>
@@ -7448,7 +7052,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>菏泽市疾病预防控制机构信息一览表信息数据量查询服务</t>
+          <t>菏泽市中心血站采血站点信息分页查询服务</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7458,7 +7062,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>菏泽市疾病预防控制机构信息一览表信息数据量查询服务</t>
+          <t>菏泽市中心血站采血站点信息分页查询服务</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7481,9 +7085,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>True</t>
@@ -7495,17 +7097,15 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2042</v>
+        <v>64</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/8c90e6707f314c5786c4a698f87b449a/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/d7f8819a676b4f16b87e986bb7a82411/detail</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -7518,7 +7118,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>菏泽市国家免费提供避孕药具发放服务点信息数据量查询服务</t>
+          <t>菏泽市疾病预防控制机构信息一览表信息分页查询服务</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7528,7 +7128,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>菏泽市国家免费提供避孕药具发放服务点信息数据量查询服务</t>
+          <t>菏泽市疾病预防控制机构信息一览表信息分页查询服务</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7551,9 +7151,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>True</t>
@@ -7565,17 +7163,15 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>114</v>
+        <v>1803</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
       </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/5a04524f9bab49c6bc3c1f6e5ebb9771/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/f750de9d283c4b619855dda0762597c7/detail</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -7588,27 +7184,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>菏泽市供销社年度安全生产工作先进个人名单信息分页查询服务</t>
+          <t>山东省农机购置补贴机具补贴额一览表信息分页查询服务</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>综合政务</t>
+          <t>市场监督</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>菏泽市供销社年度安全生产工作先进个人名单信息分页查询服务</t>
+          <t>山东省农机购置补贴机具补贴额一览表信息分页查询服务</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>菏泽市供销合作社</t>
+          <t>菏泽市农业机械服务中心</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2020-01-09</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7621,9 +7217,7 @@
           <t>无条件开放</t>
         </is>
       </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>True</t>
@@ -7635,230 +7229,18 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
-          <t>https://data.sd.gov.cn/portal/api/612f3697875a459dadcc0e6f08b52371/detail</t>
+          <t>https://data.sd.gov.cn/portal/api/fe70534f93d84f1bb2638c21cfae5cde/detail</t>
         </is>
       </c>
       <c r="P103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>菏泽市</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>菏泽市临时救助数据统计表信息数据量查询服务</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>综合政务</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>菏泽市临时救助数据统计表信息数据量查询服务</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>菏泽市民政局</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2020-01-09</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>['接口']</t>
-        </is>
-      </c>
-      <c r="L104" t="n">
-        <v>3547</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>https://data.sd.gov.cn/portal/api/03f562dd0898440daffef4c89906457e/detail</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>菏泽市</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>山东省农机购置补贴机具补贴额一览表信息分页查询服务</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>市场监督</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>山东省农机购置补贴机具补贴额一览表信息分页查询服务</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>菏泽市农业机械服务中心</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2020-01-09</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>['接口']</t>
-        </is>
-      </c>
-      <c r="L105" t="n">
-        <v>162</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>https://data.sd.gov.cn/portal/api/fe70534f93d84f1bb2638c21cfae5cde/detail</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>菏泽市</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>菏泽市级病残儿医学鉴定神经科清单信息分页查询服务</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>卫生健康</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>菏泽市级病残儿医学鉴定神经科清单信息分页查询服务</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>菏泽市卫生健康委员会</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2019-03-05</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>无条件开放</t>
-        </is>
-      </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>['接口']</t>
-        </is>
-      </c>
-      <c r="L106" t="n">
-        <v>23</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>https://data.sd.gov.cn/portal/api/29069a21de9146eeae78e96e7dc1bf3e/detail</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
